--- a/kronshtatsky/стены/PDF/6.2-Ст-К строительная леса/walls-k.xlsx
+++ b/kronshtatsky/стены/PDF/6.2-Ст-К строительная леса/walls-k.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Linux\Documents\schools\kronshtatsky\walls\PDF\6.2-Ст-К строительная леса\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Linux\Documents\schools\kronshtatsky\стены\PDF\6.2-Ст-К строительная леса\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20632,7 +20632,7 @@
       <c r="T4" s="169"/>
       <c r="U4" s="108"/>
     </row>
-    <row r="5" spans="1:21" ht="129.6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="144" x14ac:dyDescent="0.25">
       <c r="A5" s="99" t="s">
         <v>75</v>
       </c>
@@ -20897,7 +20897,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="100.8" x14ac:dyDescent="0.25">
       <c r="A10" s="102" t="s">
         <v>232</v>
       </c>
@@ -20950,7 +20950,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="100.8" x14ac:dyDescent="0.25">
       <c r="A11" s="102" t="s">
         <v>235</v>
       </c>
@@ -24039,7 +24039,7 @@
       </c>
       <c r="AH7" s="95"/>
     </row>
-    <row r="8" spans="1:34" ht="172.8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:34" ht="187.2" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>288</v>
       </c>
@@ -24213,7 +24213,7 @@
       </c>
       <c r="AH10" s="95"/>
     </row>
-    <row r="11" spans="1:34" ht="172.8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:34" ht="187.2" x14ac:dyDescent="0.25">
       <c r="A11" s="57" t="s">
         <v>292</v>
       </c>
@@ -25068,7 +25068,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="115.2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" ht="129.6" x14ac:dyDescent="0.25">
       <c r="A15" s="102" t="s">
         <v>299</v>
       </c>
@@ -26791,7 +26791,7 @@
       <c r="V7" s="78"/>
       <c r="AK7" s="95"/>
     </row>
-    <row r="8" spans="1:37" ht="172.8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" ht="187.2" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>346</v>
       </c>
@@ -27086,7 +27086,7 @@
       <c r="V12" s="78"/>
       <c r="AK12" s="95"/>
     </row>
-    <row r="13" spans="1:37" ht="172.8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37" ht="187.2" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>352</v>
       </c>
@@ -27338,7 +27338,7 @@
       </c>
       <c r="E3" s="154">
         <f>C15</f>
-        <v>2258.46</v>
+        <v>1802.53</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -27369,8 +27369,8 @@
         <v>395</v>
       </c>
       <c r="C6" s="161">
-        <f>11*7.5*2+2.5*2*10+120.31+201.62+14*2*7.5+3*2*2.5</f>
-        <v>761.93000000000006</v>
+        <f>14*2*7.5+3*2*2.5+81</f>
+        <v>306</v>
       </c>
       <c r="D6" s="178"/>
       <c r="E6" s="179"/>
@@ -27494,7 +27494,7 @@
       </c>
       <c r="C15" s="162">
         <f>SUM(C6:C14)</f>
-        <v>2258.46</v>
+        <v>1802.53</v>
       </c>
       <c r="D15" s="178"/>
       <c r="E15" s="179"/>
@@ -30337,7 +30337,7 @@
       </c>
       <c r="AC7" s="95"/>
     </row>
-    <row r="8" spans="1:29" ht="129.6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="144" x14ac:dyDescent="0.25">
       <c r="A8" s="102" t="s">
         <v>75</v>
       </c>
@@ -34990,7 +34990,7 @@
       <c r="T4" s="169"/>
       <c r="U4" s="134"/>
     </row>
-    <row r="5" spans="1:21" ht="129.6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="144" x14ac:dyDescent="0.25">
       <c r="A5" s="99" t="s">
         <v>75</v>
       </c>
@@ -35255,7 +35255,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="100.8" x14ac:dyDescent="0.25">
       <c r="A10" s="102" t="s">
         <v>232</v>
       </c>
@@ -35308,7 +35308,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="100.8" x14ac:dyDescent="0.25">
       <c r="A11" s="102" t="s">
         <v>235</v>
       </c>
@@ -37758,7 +37758,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="57" spans="1:21" ht="172.8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:21" ht="187.2" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
         <v>288</v>
       </c>
@@ -37929,7 +37929,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="60" spans="1:21" ht="172.8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:21" ht="187.2" x14ac:dyDescent="0.25">
       <c r="A60" s="57" t="s">
         <v>292</v>
       </c>
@@ -38782,7 +38782,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="115.2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" ht="129.6" x14ac:dyDescent="0.25">
       <c r="A15" s="102" t="s">
         <v>299</v>
       </c>
@@ -39695,7 +39695,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="172.8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" ht="187.2" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>346</v>
       </c>
@@ -39980,7 +39980,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:21" ht="172.8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" ht="187.2" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
         <v>352</v>
       </c>
@@ -40720,7 +40720,7 @@
       </c>
       <c r="AC7" s="95"/>
     </row>
-    <row r="8" spans="1:29" ht="129.6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="144" x14ac:dyDescent="0.25">
       <c r="A8" s="102" t="s">
         <v>75</v>
       </c>
